--- a/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v4.xlsx
+++ b/resources/excel_templates/gb_t_32151_34_2024_appendix_b_v4.xlsx
@@ -2689,19 +2689,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="9">
-    <dataValidation sqref="D4:D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 C 列。" type="custom">
+    <dataValidation sqref="D4:D18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 D 列。" type="custom">
       <formula1>OR($E4="实测值",D4="")</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请选择有效选项" error="此字段只能从下拉列表中选择。" type="list">
       <formula1>"计算值,实测值"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 E 列。" type="custom">
+    <dataValidation sqref="F4:F18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 F 列。" type="custom">
       <formula1>OR($G4="计算值",$G4="实测值",F4="")</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请选择有效选项" error="此字段只能从下拉列表中选择。" type="list">
       <formula1>"缺省值,计算值,实测值"</formula1>
     </dataValidation>
-    <dataValidation sqref="I4:I18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 H 列。" type="custom">
+    <dataValidation sqref="I4:I18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="当前不能填写" error="仅在相应数据来源选择“实测值”后可填写 I 列。" type="custom">
       <formula1>OR($J4="计算值",$J4="实测值",I4="")</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请核实填写值" error="请选择本列允许的选项。" type="list">
@@ -4094,7 +4094,7 @@
     <dataValidation sqref="I3:I8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="请核实填写值" error="请选择本列允许的选项。" type="list">
       <formula1>"目录,自定义"</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请选择因子来源" error="请选择缺省值、计算值或实测值。" type="list" errorStyle="stop">
+    <dataValidation sqref="J3:J8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="请选择因子来源" error="请选择缺省值或实测值。" type="list" errorStyle="stop">
       <formula1>"缺省值,实测值"</formula1>
     </dataValidation>
   </dataValidations>
